--- a/clustering/RU vs KZ/KZ sectors.xlsx
+++ b/clustering/RU vs KZ/KZ sectors.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Albert\.spyder-py3\ITMO-3\datasets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Albert\.spyder-py3\ITMO-3\clustering\RU vs KZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
   </bookViews>
   <sheets>
     <sheet name="All sectors" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="28">
   <si>
     <t>sector</t>
   </si>
@@ -83,6 +83,36 @@
   </si>
   <si>
     <t>Медиана</t>
+  </si>
+  <si>
+    <t>Медианы секторов (Казахстан)</t>
+  </si>
+  <si>
+    <t>Добыча</t>
+  </si>
+  <si>
+    <t>Промышленность</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Недвижимость</t>
+  </si>
+  <si>
+    <t>Наука</t>
+  </si>
+  <si>
+    <t>Сельхоз</t>
+  </si>
+  <si>
+    <t>Логистика</t>
+  </si>
+  <si>
+    <t>Коммуналка</t>
+  </si>
+  <si>
+    <t>Административный</t>
   </si>
 </sst>
 </file>
@@ -188,6 +218,942 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'All sectors'!$B$57:$B$66</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Добыча</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Промышленность</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Недвижимость</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Наука</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Сельхоз</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Строительство</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Логистика</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Коммуналка</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Административный</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'All sectors'!$C$57:$C$66</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1862064.4055999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10832458.244999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10469620.812000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6304234.7850000011</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2913359.87</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3279622.7940000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4765552.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4917959.9280000003</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1234589.98</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1886286.425</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-28F4-4AAB-A84E-E0221FCA146B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1805545935"/>
+        <c:axId val="1805546351"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="1805545935"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1805546351"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1805546351"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1805545935"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>201705</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>124384</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>425823</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>168087</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -475,7 +1441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="88.28515625" customWidth="1"/>
@@ -1525,8 +2491,273 @@
         <v>37.648800000000001</v>
       </c>
     </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" s="2">
+        <v>1862064.4055999999</v>
+      </c>
+      <c r="D57" s="2">
+        <v>7308</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4.3103448275862072E-2</v>
+      </c>
+      <c r="F57" s="2">
+        <v>168206.56020000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C58" s="2">
+        <v>10832458.244999999</v>
+      </c>
+      <c r="D58" s="2">
+        <v>1571</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2.178649237472767E-2</v>
+      </c>
+      <c r="F58" s="2">
+        <v>67742.100000000006</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59" s="2">
+        <v>10469620.812000001</v>
+      </c>
+      <c r="D59" s="2">
+        <v>10340</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2.059961315280464E-2</v>
+      </c>
+      <c r="F59" s="2">
+        <v>52849.761000000013</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C60" s="2">
+        <v>6304234.7850000011</v>
+      </c>
+      <c r="D60" s="2">
+        <v>10326</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5.2277157540315438E-3</v>
+      </c>
+      <c r="F60" s="2">
+        <v>3791.2446</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C61" s="2">
+        <v>2913359.87</v>
+      </c>
+      <c r="D61" s="2">
+        <v>14609</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1.8276404955849139E-2</v>
+      </c>
+      <c r="F61" s="2">
+        <v>28864.8855</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="2">
+        <v>3279622.7940000002</v>
+      </c>
+      <c r="D62" s="2">
+        <v>8114</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3.9438008380576779E-3</v>
+      </c>
+      <c r="F62" s="2">
+        <v>1927.5419999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" s="2">
+        <v>4765552.5</v>
+      </c>
+      <c r="D63" s="2">
+        <v>19371</v>
+      </c>
+      <c r="E63" s="3">
+        <v>1.133648756265517E-2</v>
+      </c>
+      <c r="F63" s="2">
+        <v>8728.0410000000011</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C64" s="2">
+        <v>4917959.9280000003</v>
+      </c>
+      <c r="D64" s="2">
+        <v>8201</v>
+      </c>
+      <c r="E64" s="3">
+        <v>1.7929375751612551E-2</v>
+      </c>
+      <c r="F64" s="2">
+        <v>27061.0458</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65" s="2">
+        <v>1234589.98</v>
+      </c>
+      <c r="D65" s="2">
+        <v>798</v>
+      </c>
+      <c r="E65" s="3">
+        <v>4.1469194312796213E-2</v>
+      </c>
+      <c r="F65" s="2">
+        <v>10113.263999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C66" s="2">
+        <v>1886286.425</v>
+      </c>
+      <c r="D66" s="2">
+        <v>11444</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1.0464591790708159E-2</v>
+      </c>
+      <c r="F66" s="2">
+        <v>7830.7875000000004</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C52">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D52">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E52">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F52">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C57:C66">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1538,7 +2769,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D52">
+  <conditionalFormatting sqref="D57:D66">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1550,7 +2781,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E52">
+  <conditionalFormatting sqref="E57:E66">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1562,7 +2793,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F52">
+  <conditionalFormatting sqref="F57:F66">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1576,6 +2807,7 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/clustering/RU vs KZ/KZ sectors.xlsx
+++ b/clustering/RU vs KZ/KZ sectors.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="31">
   <si>
     <t>sector</t>
   </si>
@@ -113,6 +113,15 @@
   </si>
   <si>
     <t>Административный</t>
+  </si>
+  <si>
+    <t>Медианы секторов (РФ)</t>
+  </si>
+  <si>
+    <t>Казахстан</t>
+  </si>
+  <si>
+    <t>РФ</t>
   </si>
 </sst>
 </file>
@@ -576,7 +585,509 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Распределение</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:t> ВДС по секторам экономики</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'All sectors'!$C$81</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>VDS_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'All sectors'!$B$105:$B$112</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Добыча</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Промышленность</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Недвижимость</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Наука</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Сельхоз</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Строительство</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Логистика</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'All sectors'!$C$105:$C$112</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.17189675357940878</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.96650460820677753</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.58197637529873547</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.2689472513170994</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.30275886782335809</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.43993269045829592</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.45400220492610821</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E36C-4EC4-B768-C83E5816B4A1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'All sectors'!$D$81</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ITusage_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'All sectors'!$B$105:$B$112</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Добыча</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Промышленность</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Недвижимость</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Наука</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Сельхоз</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Строительство</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Логистика</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'All sectors'!$D$105:$D$112</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.23909221105397971</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.87525754686183355</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.66866212817380788</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.30698749074179937</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.23562909901325846</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.33066611516635985</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.45264393486741733</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E36C-4EC4-B768-C83E5816B4A1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="814058416"/>
+        <c:axId val="814057168"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="814058416"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="814057168"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="814057168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="814058416"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1121,6 +1632,511 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -1148,6 +2164,36 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>268941</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>158002</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>56029</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>33618</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1441,7 +2487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="88.28515625" customWidth="1"/>
@@ -2708,9 +3754,623 @@
         <v>7830.7875000000004</v>
       </c>
     </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C71" s="2">
+        <v>1862064.4055999999</v>
+      </c>
+      <c r="D71" s="2">
+        <v>7308</v>
+      </c>
+      <c r="E71" s="3">
+        <v>4.3103448275862072E-2</v>
+      </c>
+      <c r="F71" s="2">
+        <v>168206.56020000001</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C72" s="2">
+        <v>10832458.244999999</v>
+      </c>
+      <c r="D72" s="2">
+        <v>1571</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2.178649237472767E-2</v>
+      </c>
+      <c r="F72" s="2">
+        <v>67742.100000000006</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C73" s="2">
+        <v>10469620.812000001</v>
+      </c>
+      <c r="D73" s="2">
+        <v>10340</v>
+      </c>
+      <c r="E73" s="3">
+        <v>2.059961315280464E-2</v>
+      </c>
+      <c r="F73" s="2">
+        <v>52849.761000000013</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C74" s="2">
+        <v>6304234.7850000011</v>
+      </c>
+      <c r="D74" s="2">
+        <v>10326</v>
+      </c>
+      <c r="E74" s="3">
+        <v>5.2277157540315438E-3</v>
+      </c>
+      <c r="F74" s="2">
+        <v>3791.2446</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C75" s="2">
+        <v>2913359.87</v>
+      </c>
+      <c r="D75" s="2">
+        <v>14609</v>
+      </c>
+      <c r="E75" s="3">
+        <v>1.8276404955849139E-2</v>
+      </c>
+      <c r="F75" s="2">
+        <v>28864.8855</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="2">
+        <v>3279622.7940000002</v>
+      </c>
+      <c r="D76" s="2">
+        <v>8114</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3.9438008380576779E-3</v>
+      </c>
+      <c r="F76" s="2">
+        <v>1927.5419999999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C77" s="2">
+        <v>4765552.5</v>
+      </c>
+      <c r="D77" s="2">
+        <v>19371</v>
+      </c>
+      <c r="E77" s="3">
+        <v>1.133648756265517E-2</v>
+      </c>
+      <c r="F77" s="2">
+        <v>8728.0410000000011</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C78" s="2">
+        <v>4917959.9280000003</v>
+      </c>
+      <c r="D78" s="2">
+        <v>8201</v>
+      </c>
+      <c r="E78" s="3">
+        <v>1.7929375751612551E-2</v>
+      </c>
+      <c r="F78" s="2">
+        <v>27061.0458</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C80" s="2">
+        <f>MAX(C71:C78)</f>
+        <v>10832458.244999999</v>
+      </c>
+      <c r="D80" s="2">
+        <f t="shared" ref="D80:F80" si="0">MAX(D71:D78)</f>
+        <v>19371</v>
+      </c>
+      <c r="E80" s="2">
+        <f t="shared" si="0"/>
+        <v>4.3103448275862072E-2</v>
+      </c>
+      <c r="F80" s="2">
+        <f t="shared" si="0"/>
+        <v>168206.56020000001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C81" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B82" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C82" s="4">
+        <f>C71/C$80</f>
+        <v>0.17189675357940878</v>
+      </c>
+      <c r="D82" s="4">
+        <f t="shared" ref="D82:F82" si="1">D71/D$80</f>
+        <v>0.37726498373857831</v>
+      </c>
+      <c r="E82" s="4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="F82" s="4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B83" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C83" s="4">
+        <f>C72/C$80</f>
+        <v>1</v>
+      </c>
+      <c r="D83" s="4">
+        <f t="shared" ref="D83:F83" si="2">D72/D$80</f>
+        <v>8.1100614320375825E-2</v>
+      </c>
+      <c r="E83" s="4">
+        <f t="shared" si="2"/>
+        <v>0.50544662309368193</v>
+      </c>
+      <c r="F83" s="4">
+        <f t="shared" si="2"/>
+        <v>0.40273161712274291</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C84" s="4">
+        <f>C73/C$80</f>
+        <v>0.96650460820677753</v>
+      </c>
+      <c r="D84" s="4">
+        <f t="shared" ref="D84:F84" si="3">D73/D$80</f>
+        <v>0.53378762067007379</v>
+      </c>
+      <c r="E84" s="4">
+        <f t="shared" si="3"/>
+        <v>0.47791102514506761</v>
+      </c>
+      <c r="F84" s="4">
+        <f t="shared" si="3"/>
+        <v>0.31419559936997044</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B85" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C85" s="4">
+        <f t="shared" ref="C85:F88" si="4">C74/C$80</f>
+        <v>0.58197637529873547</v>
+      </c>
+      <c r="D85" s="4">
+        <f t="shared" si="4"/>
+        <v>0.53306489081616848</v>
+      </c>
+      <c r="E85" s="4">
+        <f t="shared" si="4"/>
+        <v>0.12128300549353181</v>
+      </c>
+      <c r="F85" s="4">
+        <f t="shared" si="4"/>
+        <v>2.2539219608867549E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B86" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C86" s="4">
+        <f t="shared" si="4"/>
+        <v>0.2689472513170994</v>
+      </c>
+      <c r="D86" s="4">
+        <f t="shared" si="4"/>
+        <v>0.7541686025502039</v>
+      </c>
+      <c r="E86" s="4">
+        <f t="shared" si="4"/>
+        <v>0.42401259497569999</v>
+      </c>
+      <c r="F86" s="4">
+        <f t="shared" si="4"/>
+        <v>0.17160380347638785</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C87" s="4">
+        <f t="shared" si="4"/>
+        <v>0.30275886782335809</v>
+      </c>
+      <c r="D87" s="4">
+        <f t="shared" si="4"/>
+        <v>0.41887357389912755</v>
+      </c>
+      <c r="E87" s="4">
+        <f t="shared" si="4"/>
+        <v>9.1496179442938114E-2</v>
+      </c>
+      <c r="F87" s="4">
+        <f t="shared" si="4"/>
+        <v>1.1459374698038679E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B88" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C88" s="4">
+        <f t="shared" si="4"/>
+        <v>0.43993269045829592</v>
+      </c>
+      <c r="D88" s="4">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="E88" s="4">
+        <f t="shared" si="4"/>
+        <v>0.26300651145359993</v>
+      </c>
+      <c r="F88" s="4">
+        <f t="shared" si="4"/>
+        <v>5.1888826390731939E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B89" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C89" s="4">
+        <f>C78/C$80</f>
+        <v>0.45400220492610821</v>
+      </c>
+      <c r="D89" s="4">
+        <f t="shared" ref="D89:F89" si="5">D78/D$80</f>
+        <v>0.42336482370553918</v>
+      </c>
+      <c r="E89" s="4">
+        <f t="shared" si="5"/>
+        <v>0.41596151743741117</v>
+      </c>
+      <c r="F89" s="4">
+        <f t="shared" si="5"/>
+        <v>0.16087984777659106</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B93" s="2"/>
+      <c r="C93" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B94" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C94" s="4">
+        <v>0.23909221105397971</v>
+      </c>
+      <c r="D94" s="4">
+        <v>0.55954614082444987</v>
+      </c>
+      <c r="E94" s="4">
+        <v>1</v>
+      </c>
+      <c r="F94" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B95" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C95" s="4">
+        <v>0.87525754686183355</v>
+      </c>
+      <c r="D95" s="4">
+        <v>0.11136020496865992</v>
+      </c>
+      <c r="E95" s="4">
+        <v>0.68607147392914902</v>
+      </c>
+      <c r="F95" s="4">
+        <v>6.8481463056614095E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B96" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C96" s="4">
+        <v>1</v>
+      </c>
+      <c r="D96" s="4">
+        <v>0.78139726403440546</v>
+      </c>
+      <c r="E96" s="4">
+        <v>0.80063757597530205</v>
+      </c>
+      <c r="F96" s="4">
+        <v>0.30837423906026395</v>
+      </c>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B97" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C97" s="4">
+        <v>0.66866212817380788</v>
+      </c>
+      <c r="D97" s="4">
+        <v>0.40261701056869653</v>
+      </c>
+      <c r="E97" s="4">
+        <v>0.55400770573728275</v>
+      </c>
+      <c r="F97" s="4">
+        <v>2.8515961341410913E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B98" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C98" s="4">
+        <v>0.30698749074179937</v>
+      </c>
+      <c r="D98" s="4">
+        <v>1</v>
+      </c>
+      <c r="E98" s="4">
+        <v>0.58433435380303211</v>
+      </c>
+      <c r="F98" s="4">
+        <v>0.21637851304519196</v>
+      </c>
+    </row>
+    <row r="99" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B99" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C99" s="4">
+        <v>0.23562909901325846</v>
+      </c>
+      <c r="D99" s="4">
+        <v>0.26252459166399783</v>
+      </c>
+      <c r="E99" s="4">
+        <v>0.64644485253175021</v>
+      </c>
+      <c r="F99" s="4">
+        <v>8.1808097742136088E-3</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B100" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C100" s="4">
+        <v>0.33066611516635985</v>
+      </c>
+      <c r="D100" s="4">
+        <v>0.3124857025209315</v>
+      </c>
+      <c r="E100" s="4">
+        <v>0.62224991381325467</v>
+      </c>
+      <c r="F100" s="4">
+        <v>2.3271437218520076E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B101" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C101" s="4">
+        <v>0.45264393486741733</v>
+      </c>
+      <c r="D101" s="4">
+        <v>0.51205563435055135</v>
+      </c>
+      <c r="E101" s="4">
+        <v>0.91469804388033071</v>
+      </c>
+      <c r="F101" s="4">
+        <v>0.18542309535056511</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B104" s="2"/>
+      <c r="C104" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B105" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C105" s="4">
+        <v>0.17189675357940878</v>
+      </c>
+      <c r="D105" s="4">
+        <v>0.23909221105397971</v>
+      </c>
+    </row>
+    <row r="106" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B106" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C106" s="4">
+        <v>1</v>
+      </c>
+      <c r="D106" s="4">
+        <v>0.87525754686183355</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B107" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C107" s="4">
+        <v>0.96650460820677753</v>
+      </c>
+      <c r="D107" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B108" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C108" s="4">
+        <v>0.58197637529873547</v>
+      </c>
+      <c r="D108" s="4">
+        <v>0.66866212817380788</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B109" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C109" s="4">
+        <v>0.2689472513170994</v>
+      </c>
+      <c r="D109" s="4">
+        <v>0.30698749074179937</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B110" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C110" s="4">
+        <v>0.30275886782335809</v>
+      </c>
+      <c r="D110" s="4">
+        <v>0.23562909901325846</v>
+      </c>
+    </row>
+    <row r="111" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B111" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C111" s="4">
+        <v>0.43993269045829592</v>
+      </c>
+      <c r="D111" s="4">
+        <v>0.33066611516635985</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B112" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C112" s="4">
+        <v>0.45400220492610821</v>
+      </c>
+      <c r="D112" s="4">
+        <v>0.45264393486741733</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C52">
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2722,7 +4382,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D52">
-    <cfRule type="colorScale" priority="7">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2734,7 +4394,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E52">
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2746,7 +4406,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F52">
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2758,7 +4418,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C57:C66">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2770,7 +4430,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D57:D66">
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2782,7 +4442,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E57:E66">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2794,7 +4454,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F57:F66">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/clustering/RU vs KZ/KZ sectors.xlsx
+++ b/clustering/RU vs KZ/KZ sectors.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="31">
   <si>
     <t>sector</t>
   </si>
@@ -608,10 +608,7 @@
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -619,14 +616,26 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ru-RU"/>
+              <a:rPr lang="ru-RU">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
               <a:t>Распределение</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:rPr lang="ru-RU" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
               <a:t> ВДС по секторам экономики</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-US">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
@@ -646,10 +655,7 @@
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -675,7 +681,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>VDS_s</c:v>
+                  <c:v>Казахстан</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -784,7 +790,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>ITusage_s</c:v>
+                  <c:v>РФ</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -924,12 +930,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1010,6 +1013,1533 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Распределение</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> затрат на внедрение </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>IT-</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>технологий по секторам экономики</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'All sectors'!$C$81</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Казахстан</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'All sectors'!$B$116:$B$123</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Добыча</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Промышленность</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Недвижимость</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Наука</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Сельхоз</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Строительство</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Логистика</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'All sectors'!$C$116:$C$123</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.40273161712274291</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.31419559936997044</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.2539219608867549E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.17160380347638785</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.1459374698038679E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.1888826390731939E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.16087984777659106</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-297C-4522-A76D-68D55F603C25}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'All sectors'!$D$81</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>РФ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'All sectors'!$B$116:$B$123</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Добыча</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Промышленность</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Недвижимость</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Наука</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Сельхоз</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Строительство</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Логистика</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'All sectors'!$D$116:$D$123</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.8481463056614095E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.30837423906026395</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.8515961341410913E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.21637851304519196</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.1808097742136088E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.3271437218520076E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.18542309535056511</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-297C-4522-A76D-68D55F603C25}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="814058416"/>
+        <c:axId val="814057168"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="814058416"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="814057168"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="814057168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="814058416"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Распределение</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> числа организаций использующих технологии сбора, обработки и анализа больших данных по секторам экономики</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'All sectors'!$C$81</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Казахстан</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'All sectors'!$B$126:$B$133</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Добыча</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Промышленность</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Недвижимость</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Наука</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Сельхоз</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Строительство</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Логистика</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'All sectors'!$C$126:$C$133</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.50544662309368193</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.47791102514506761</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.12128300549353181</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.42401259497569999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.1496179442938114E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.26300651145359993</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.41596151743741117</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CC90-4837-BC89-0032B236F324}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'All sectors'!$D$81</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>РФ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'All sectors'!$B$126:$B$133</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Добыча</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Промышленность</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Недвижимость</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Наука</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Сельхоз</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Строительство</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Логистика</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'All sectors'!$D$126:$D$133</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.68607147392914902</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.80063757597530205</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.55400770573728275</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.58433435380303211</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.64644485253175021</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.62224991381325467</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.91469804388033071</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-CC90-4837-BC89-0032B236F324}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="814058416"/>
+        <c:axId val="814057168"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="814058416"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="814057168"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="814057168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="814058416"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Распределение</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> числа организаций использующих цифровые технологии по секторам экономики</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'All sectors'!$C$81</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Казахстан</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'All sectors'!$B$136:$B$143</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Добыча</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Промышленность</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Недвижимость</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Наука</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Сельхоз</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Строительство</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Логистика</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'All sectors'!$C$136:$C$143</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.37726498373857831</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.1100614320375825E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.53378762067007379</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.53306489081616848</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.7541686025502039</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.41887357389912755</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.42336482370553918</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AA27-4A4A-BF3A-8CB1F5EB21E3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'All sectors'!$D$81</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>РФ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'All sectors'!$B$136:$B$143</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Добыча</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Промышленность</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Недвижимость</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Наука</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Сельхоз</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Строительство</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Логистика</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'All sectors'!$D$136:$D$143</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.55954614082444987</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.11136020496865992</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.78139726403440546</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.40261701056869653</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.26252459166399783</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.3124857025209315</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.51205563435055135</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-AA27-4A4A-BF3A-8CB1F5EB21E3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="814058416"/>
+        <c:axId val="814057168"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="814058416"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="814057168"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="814057168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="814058416"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1127,6 +2657,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
   <cs:axisTitle>
@@ -1633,6 +3283,1521 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2194,6 +5359,102 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>336176</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>56029</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>123264</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>122145</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Диаграмма 3"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>324971</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>134470</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>112059</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>10086</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Диаграмма 4"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>44823</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>168088</xdr:colOff>
+      <xdr:row>174</xdr:row>
+      <xdr:rowOff>110939</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Диаграмма 5"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2487,7 +5748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:H143"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="88.28515625" customWidth="1"/>
@@ -3933,12 +7194,12 @@
         <v>168206.56020000001</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C81" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>3</v>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C81" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>4</v>
@@ -3946,8 +7207,10 @@
       <c r="F81" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G81" s="5"/>
+      <c r="H81" s="5"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B82" s="2" t="s">
         <v>21</v>
       </c>
@@ -3968,7 +7231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B83" s="2" t="s">
         <v>19</v>
       </c>
@@ -3989,7 +7252,7 @@
         <v>0.40273161712274291</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B84" s="2" t="s">
         <v>20</v>
       </c>
@@ -4010,7 +7273,7 @@
         <v>0.31419559936997044</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B85" s="2" t="s">
         <v>22</v>
       </c>
@@ -4031,7 +7294,7 @@
         <v>2.2539219608867549E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B86" s="2" t="s">
         <v>23</v>
       </c>
@@ -4052,7 +7315,7 @@
         <v>0.17160380347638785</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B87" s="2" t="s">
         <v>24</v>
       </c>
@@ -4073,7 +7336,7 @@
         <v>1.1459374698038679E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B88" s="2" t="s">
         <v>14</v>
       </c>
@@ -4094,7 +7357,7 @@
         <v>5.1888826390731939E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B89" s="2" t="s">
         <v>25</v>
       </c>
@@ -4115,12 +7378,12 @@
         <v>0.16087984777659106</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B93" s="2"/>
       <c r="C93" s="5" t="s">
         <v>2</v>
@@ -4135,7 +7398,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B94" s="2" t="s">
         <v>21</v>
       </c>
@@ -4152,7 +7415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B95" s="2" t="s">
         <v>19</v>
       </c>
@@ -4169,7 +7432,7 @@
         <v>6.8481463056614095E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B96" s="2" t="s">
         <v>20</v>
       </c>
@@ -4272,7 +7535,9 @@
       </c>
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B104" s="2"/>
+      <c r="B104" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="C104" s="5" t="s">
         <v>29</v>
       </c>
@@ -4366,6 +7631,303 @@
       </c>
       <c r="D112" s="4">
         <v>0.45264393486741733</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B115" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B116" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C116" s="4">
+        <v>1</v>
+      </c>
+      <c r="D116" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B117" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C117" s="4">
+        <v>0.40273161712274291</v>
+      </c>
+      <c r="D117" s="4">
+        <v>6.8481463056614095E-2</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B118" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C118" s="4">
+        <v>0.31419559936997044</v>
+      </c>
+      <c r="D118" s="4">
+        <v>0.30837423906026395</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B119" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C119" s="4">
+        <v>2.2539219608867549E-2</v>
+      </c>
+      <c r="D119" s="4">
+        <v>2.8515961341410913E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B120" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C120" s="4">
+        <v>0.17160380347638785</v>
+      </c>
+      <c r="D120" s="4">
+        <v>0.21637851304519196</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B121" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C121" s="4">
+        <v>1.1459374698038679E-2</v>
+      </c>
+      <c r="D121" s="4">
+        <v>8.1808097742136088E-3</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B122" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C122" s="4">
+        <v>5.1888826390731939E-2</v>
+      </c>
+      <c r="D122" s="4">
+        <v>2.3271437218520076E-2</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B123" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C123" s="4">
+        <v>0.16087984777659106</v>
+      </c>
+      <c r="D123" s="4">
+        <v>0.18542309535056511</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B125" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B126" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C126" s="4">
+        <v>1</v>
+      </c>
+      <c r="D126" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B127" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C127" s="4">
+        <v>0.50544662309368193</v>
+      </c>
+      <c r="D127" s="4">
+        <v>0.68607147392914902</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B128" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C128" s="4">
+        <v>0.47791102514506761</v>
+      </c>
+      <c r="D128" s="4">
+        <v>0.80063757597530205</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B129" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C129" s="4">
+        <v>0.12128300549353181</v>
+      </c>
+      <c r="D129" s="4">
+        <v>0.55400770573728275</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B130" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C130" s="4">
+        <v>0.42401259497569999</v>
+      </c>
+      <c r="D130" s="4">
+        <v>0.58433435380303211</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B131" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C131" s="4">
+        <v>9.1496179442938114E-2</v>
+      </c>
+      <c r="D131" s="4">
+        <v>0.64644485253175021</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B132" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C132" s="4">
+        <v>0.26300651145359993</v>
+      </c>
+      <c r="D132" s="4">
+        <v>0.62224991381325467</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B133" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C133" s="4">
+        <v>0.41596151743741117</v>
+      </c>
+      <c r="D133" s="4">
+        <v>0.91469804388033071</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B135" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B136" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C136" s="4">
+        <v>0.37726498373857831</v>
+      </c>
+      <c r="D136" s="4">
+        <v>0.55954614082444987</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B137" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C137" s="4">
+        <v>8.1100614320375825E-2</v>
+      </c>
+      <c r="D137" s="4">
+        <v>0.11136020496865992</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B138" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C138" s="4">
+        <v>0.53378762067007379</v>
+      </c>
+      <c r="D138" s="4">
+        <v>0.78139726403440546</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B139" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C139" s="4">
+        <v>0.53306489081616848</v>
+      </c>
+      <c r="D139" s="4">
+        <v>0.40261701056869653</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B140" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C140" s="4">
+        <v>0.7541686025502039</v>
+      </c>
+      <c r="D140" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B141" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C141" s="4">
+        <v>0.41887357389912755</v>
+      </c>
+      <c r="D141" s="4">
+        <v>0.26252459166399783</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B142" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C142" s="4">
+        <v>1</v>
+      </c>
+      <c r="D142" s="4">
+        <v>0.3124857025209315</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B143" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C143" s="4">
+        <v>0.42336482370553918</v>
+      </c>
+      <c r="D143" s="4">
+        <v>0.51205563435055135</v>
       </c>
     </row>
   </sheetData>
